--- a/data/reports/PHASE_8_SKIP_TRACKER.xlsx
+++ b/data/reports/PHASE_8_SKIP_TRACKER.xlsx
@@ -462,7 +462,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -484,7 +484,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="D3" t="n">
         <v>140</v>
@@ -506,7 +506,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -550,7 +550,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
@@ -594,7 +594,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="D9" t="n">
         <v>534</v>
@@ -638,7 +638,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D10" t="n">
         <v>341</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -682,7 +682,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D12" t="n">
         <v>158.25</v>
@@ -704,7 +704,7 @@
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D13" t="n">
         <v>130.5</v>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D15" t="n">
         <v>87.75</v>
@@ -770,7 +770,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D16" t="n">
         <v>313.67</v>
@@ -792,7 +792,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D17" t="n">
         <v>189</v>
@@ -814,7 +814,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D18" t="n">
         <v>441</v>
@@ -836,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D19" t="n">
         <v>479</v>
@@ -851,64 +851,64 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>047</t>
+          <t>229</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="D20" t="n">
-        <v>169.17</v>
+        <v>297.33</v>
       </c>
       <c r="E20" t="n">
-        <v>315</v>
+        <v>451</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>45827</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>224</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D21" t="n">
-        <v>297.33</v>
+        <v>260</v>
       </c>
       <c r="E21" t="n">
-        <v>451</v>
+        <v>381</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>45832</v>
+        <v>45836</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D22" t="n">
-        <v>260</v>
+        <v>221</v>
       </c>
       <c r="E22" t="n">
-        <v>381</v>
+        <v>462</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>45836</v>
@@ -917,284 +917,284 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>779</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D23" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E23" t="n">
-        <v>462</v>
+        <v>588</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>45836</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>658</v>
+        <v>634</v>
       </c>
       <c r="D24" t="n">
-        <v>227</v>
+        <v>92.36</v>
       </c>
       <c r="E24" t="n">
-        <v>588</v>
+        <v>259</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>45840</v>
+        <v>45853</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>477</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="D25" t="n">
-        <v>92.36</v>
+        <v>432</v>
       </c>
       <c r="E25" t="n">
-        <v>259</v>
+        <v>542</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>45853</v>
+        <v>45865</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>256</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C26" t="n">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="D26" t="n">
-        <v>432</v>
+        <v>128.11</v>
       </c>
       <c r="E26" t="n">
-        <v>542</v>
+        <v>200</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>45865</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="D27" t="n">
-        <v>128.11</v>
+        <v>194.83</v>
       </c>
       <c r="E27" t="n">
-        <v>200</v>
+        <v>291</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>45869</v>
+        <v>45883</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>899</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="D28" t="n">
-        <v>194.83</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>45883</v>
+        <v>45890</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>667</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>45890</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>008</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="D30" t="n">
-        <v>299</v>
+        <v>380</v>
       </c>
       <c r="E30" t="n">
-        <v>395</v>
+        <v>647</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>45891</v>
+        <v>45894</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="D31" t="n">
-        <v>380</v>
+        <v>225.25</v>
       </c>
       <c r="E31" t="n">
-        <v>647</v>
+        <v>314</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>45894</v>
+        <v>45899</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>557</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C32" t="n">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D32" t="n">
-        <v>225.25</v>
+        <v>167.43</v>
       </c>
       <c r="E32" t="n">
-        <v>314</v>
+        <v>464</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>45899</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>189</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C33" t="n">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="D33" t="n">
-        <v>167.43</v>
+        <v>91.08</v>
       </c>
       <c r="E33" t="n">
-        <v>464</v>
+        <v>427</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>45901</v>
+        <v>45906</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>188</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D34" t="n">
-        <v>91.08</v>
+        <v>253.25</v>
       </c>
       <c r="E34" t="n">
-        <v>427</v>
+        <v>359</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>45906</v>
+        <v>45912</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C35" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D35" t="n">
-        <v>253.25</v>
+        <v>120.67</v>
       </c>
       <c r="E35" t="n">
-        <v>359</v>
+        <v>227</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>45912</v>
@@ -1203,139 +1203,139 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>999</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D36" t="n">
-        <v>120.67</v>
+        <v>312.5</v>
       </c>
       <c r="E36" t="n">
-        <v>227</v>
+        <v>435</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>144</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C37" t="n">
-        <v>506</v>
+        <v>476</v>
       </c>
       <c r="D37" t="n">
-        <v>312.5</v>
+        <v>178.86</v>
       </c>
       <c r="E37" t="n">
-        <v>435</v>
+        <v>367</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>45916</v>
+        <v>45932</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C38" t="n">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="D38" t="n">
-        <v>178.86</v>
+        <v>116.36</v>
       </c>
       <c r="E38" t="n">
-        <v>367</v>
+        <v>328</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>777</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
         <v>467</v>
       </c>
       <c r="D39" t="n">
-        <v>116.36</v>
+        <v>485</v>
       </c>
       <c r="E39" t="n">
-        <v>328</v>
+        <v>968</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C40" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D40" t="n">
-        <v>485</v>
+        <v>117.45</v>
       </c>
       <c r="E40" t="n">
-        <v>968</v>
+        <v>271</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D41" t="n">
-        <v>117.45</v>
+        <v>935</v>
       </c>
       <c r="E41" t="n">
-        <v>271</v>
+        <v>935</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>45939</v>
+        <v>45942</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>000</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1345,362 +1345,362 @@
         <v>454</v>
       </c>
       <c r="D42" t="n">
-        <v>935</v>
+        <v>836</v>
       </c>
       <c r="E42" t="n">
-        <v>935</v>
+        <v>836</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>45942</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>000</t>
+          <t>002</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="D43" t="n">
-        <v>836</v>
+        <v>466.5</v>
       </c>
       <c r="E43" t="n">
-        <v>836</v>
+        <v>793</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>45943</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>248</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C44" t="n">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D44" t="n">
-        <v>466.5</v>
+        <v>164</v>
       </c>
       <c r="E44" t="n">
-        <v>793</v>
+        <v>577</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C45" t="n">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="D45" t="n">
-        <v>164</v>
+        <v>216.5</v>
       </c>
       <c r="E45" t="n">
-        <v>577</v>
+        <v>533</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>45957</v>
+        <v>45963</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>048</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C46" t="n">
         <v>412</v>
       </c>
       <c r="D46" t="n">
-        <v>216.5</v>
+        <v>163.75</v>
       </c>
       <c r="E46" t="n">
-        <v>533</v>
+        <v>292</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>45963</v>
+        <v>45964</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>048</t>
+          <t>788</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D47" t="n">
-        <v>163.75</v>
+        <v>143.75</v>
       </c>
       <c r="E47" t="n">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>45964</v>
+        <v>45968</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="D48" t="n">
-        <v>143.75</v>
+        <v>438</v>
       </c>
       <c r="E48" t="n">
-        <v>337</v>
+        <v>524</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>45968</v>
+        <v>45973</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C49" t="n">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D49" t="n">
-        <v>438</v>
+        <v>211.83</v>
       </c>
       <c r="E49" t="n">
-        <v>524</v>
+        <v>339</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D50" t="n">
-        <v>211.83</v>
+        <v>297.5</v>
       </c>
       <c r="E50" t="n">
-        <v>339</v>
+        <v>431</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>45975</v>
+        <v>45977</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>066</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C51" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D51" t="n">
-        <v>297.5</v>
+        <v>269.4</v>
       </c>
       <c r="E51" t="n">
-        <v>431</v>
+        <v>803</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>45977</v>
+        <v>45978</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>445</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D52" t="n">
-        <v>269.4</v>
+        <v>143.22</v>
       </c>
       <c r="E52" t="n">
-        <v>803</v>
+        <v>593</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D53" t="n">
-        <v>143.22</v>
+        <v>587</v>
       </c>
       <c r="E53" t="n">
-        <v>593</v>
+        <v>816</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>168</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>3</v>
       </c>
       <c r="C54" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D54" t="n">
-        <v>587</v>
+        <v>302</v>
       </c>
       <c r="E54" t="n">
-        <v>816</v>
+        <v>423</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>45981</v>
+        <v>45983</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>225</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="D55" t="n">
-        <v>302</v>
+        <v>775</v>
       </c>
       <c r="E55" t="n">
-        <v>423</v>
+        <v>775</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>45983</v>
+        <v>45988</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>233</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C56" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D56" t="n">
-        <v>775</v>
+        <v>217.33</v>
       </c>
       <c r="E56" t="n">
-        <v>775</v>
+        <v>483</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>45988</v>
+        <v>45989</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>789</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C57" t="n">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D57" t="n">
-        <v>217.33</v>
+        <v>185.86</v>
       </c>
       <c r="E57" t="n">
-        <v>483</v>
+        <v>416</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>223</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C58" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D58" t="n">
-        <v>185.86</v>
+        <v>658.5</v>
       </c>
       <c r="E58" t="n">
-        <v>416</v>
+        <v>1051</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>45992</v>
@@ -1709,64 +1709,64 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>677</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C59" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D59" t="n">
-        <v>658.5</v>
+        <v>323.75</v>
       </c>
       <c r="E59" t="n">
-        <v>1051</v>
+        <v>718</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C60" t="n">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D60" t="n">
-        <v>323.75</v>
+        <v>166.75</v>
       </c>
       <c r="E60" t="n">
-        <v>718</v>
+        <v>506</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>45994</v>
+        <v>45997</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>014</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C61" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D61" t="n">
-        <v>166.75</v>
+        <v>111.5</v>
       </c>
       <c r="E61" t="n">
-        <v>506</v>
+        <v>207</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>45997</v>
@@ -1775,42 +1775,42 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>367</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C62" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D62" t="n">
-        <v>111.5</v>
+        <v>140</v>
       </c>
       <c r="E62" t="n">
-        <v>207</v>
+        <v>256</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>45997</v>
+        <v>45999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>088</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D63" t="n">
-        <v>140</v>
+        <v>1364</v>
       </c>
       <c r="E63" t="n">
-        <v>256</v>
+        <v>1364</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>45999</v>
@@ -1819,117 +1819,117 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>088</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C64" t="n">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="D64" t="n">
-        <v>1364</v>
+        <v>258.6</v>
       </c>
       <c r="E64" t="n">
-        <v>1364</v>
+        <v>779</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>45999</v>
+        <v>46013</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>344</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C65" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D65" t="n">
-        <v>258.6</v>
+        <v>222</v>
       </c>
       <c r="E65" t="n">
-        <v>779</v>
+        <v>656</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>599</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C66" t="n">
         <v>310</v>
       </c>
       <c r="D66" t="n">
-        <v>222</v>
+        <v>279.8</v>
       </c>
       <c r="E66" t="n">
-        <v>656</v>
+        <v>384</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>578</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C67" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D67" t="n">
-        <v>279.8</v>
+        <v>141.1</v>
       </c>
       <c r="E67" t="n">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C68" t="n">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="D68" t="n">
-        <v>141.1</v>
+        <v>290</v>
       </c>
       <c r="E68" t="n">
-        <v>409</v>
+        <v>771</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46017</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>077</t>
+          <t>336</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1939,54 +1939,54 @@
         <v>294</v>
       </c>
       <c r="D69" t="n">
-        <v>290</v>
+        <v>276.6</v>
       </c>
       <c r="E69" t="n">
-        <v>771</v>
+        <v>842</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>478</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" t="n">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D70" t="n">
-        <v>276.6</v>
+        <v>190.5</v>
       </c>
       <c r="E70" t="n">
-        <v>842</v>
+        <v>302</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46024</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C71" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D71" t="n">
-        <v>190.5</v>
+        <v>123.09</v>
       </c>
       <c r="E71" t="n">
-        <v>302</v>
+        <v>399</v>
       </c>
       <c r="F71" s="1" t="n">
         <v>46029</v>
@@ -1995,108 +1995,108 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C72" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D72" t="n">
-        <v>123.09</v>
+        <v>220.5</v>
       </c>
       <c r="E72" t="n">
-        <v>399</v>
+        <v>337</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>055</t>
+          <t>028</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C73" t="n">
         <v>281</v>
       </c>
       <c r="D73" t="n">
-        <v>220.5</v>
+        <v>171.25</v>
       </c>
       <c r="E73" t="n">
-        <v>337</v>
+        <v>694</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>028</t>
+          <t>355</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C74" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D74" t="n">
-        <v>171.25</v>
+        <v>250.33</v>
       </c>
       <c r="E74" t="n">
-        <v>694</v>
+        <v>469</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46031</v>
+        <v>46033</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C75" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D75" t="n">
-        <v>250.33</v>
+        <v>112.17</v>
       </c>
       <c r="E75" t="n">
-        <v>469</v>
+        <v>249</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46033</v>
+        <v>46035</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>456</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C76" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D76" t="n">
-        <v>112.17</v>
+        <v>163.22</v>
       </c>
       <c r="E76" t="n">
-        <v>249</v>
+        <v>438</v>
       </c>
       <c r="F76" s="1" t="n">
         <v>46035</v>
@@ -2105,218 +2105,218 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>018</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C77" t="n">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D77" t="n">
-        <v>163.22</v>
+        <v>121.2</v>
       </c>
       <c r="E77" t="n">
-        <v>438</v>
+        <v>310</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46035</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>559</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C78" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D78" t="n">
-        <v>121.2</v>
+        <v>358</v>
       </c>
       <c r="E78" t="n">
-        <v>310</v>
+        <v>881</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46038</v>
+        <v>46040</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>044</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C79" t="n">
         <v>261</v>
       </c>
       <c r="D79" t="n">
-        <v>358</v>
+        <v>347.33</v>
       </c>
       <c r="E79" t="n">
-        <v>881</v>
+        <v>552</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46040</v>
+        <v>46041</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C80" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D80" t="n">
-        <v>347.33</v>
+        <v>120.91</v>
       </c>
       <c r="E80" t="n">
-        <v>552</v>
+        <v>490</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46041</v>
+        <v>46044</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>567</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>12</v>
       </c>
       <c r="C81" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D81" t="n">
-        <v>120.91</v>
+        <v>112.45</v>
       </c>
       <c r="E81" t="n">
-        <v>490</v>
+        <v>555</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>447</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C82" t="n">
         <v>250</v>
       </c>
       <c r="D82" t="n">
-        <v>112.45</v>
+        <v>155.33</v>
       </c>
       <c r="E82" t="n">
-        <v>555</v>
+        <v>495</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46045</v>
+        <v>46046</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>227</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D83" t="n">
-        <v>155.33</v>
+        <v>938</v>
       </c>
       <c r="E83" t="n">
-        <v>495</v>
+        <v>938</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>46046</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>448</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C84" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D84" t="n">
-        <v>938</v>
+        <v>290.2</v>
       </c>
       <c r="E84" t="n">
-        <v>938</v>
+        <v>510</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>689</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C85" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D85" t="n">
-        <v>290.2</v>
+        <v>128.73</v>
       </c>
       <c r="E85" t="n">
-        <v>510</v>
+        <v>361</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>46050</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C86" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D86" t="n">
-        <v>128.73</v>
+        <v>279</v>
       </c>
       <c r="E86" t="n">
-        <v>361</v>
+        <v>759</v>
       </c>
       <c r="F86" s="1" t="n">
         <v>46053</v>
@@ -2325,42 +2325,42 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>199</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C87" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D87" t="n">
-        <v>279</v>
+        <v>176.57</v>
       </c>
       <c r="E87" t="n">
-        <v>759</v>
+        <v>570</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C88" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D88" t="n">
-        <v>176.57</v>
+        <v>210.6</v>
       </c>
       <c r="E88" t="n">
-        <v>570</v>
+        <v>645</v>
       </c>
       <c r="F88" s="1" t="n">
         <v>46054</v>
@@ -2369,95 +2369,95 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>033</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C89" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D89" t="n">
-        <v>210.6</v>
+        <v>170.57</v>
       </c>
       <c r="E89" t="n">
-        <v>645</v>
+        <v>479</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>46054</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>236</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C90" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D90" t="n">
-        <v>170.57</v>
+        <v>280.2</v>
       </c>
       <c r="E90" t="n">
-        <v>479</v>
+        <v>592</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>46057</v>
+        <v>46060</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>556</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D91" t="n">
-        <v>280.2</v>
+        <v>1250</v>
       </c>
       <c r="E91" t="n">
-        <v>592</v>
+        <v>1250</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>46060</v>
+        <v>46061</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>266</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C92" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D92" t="n">
-        <v>1250</v>
+        <v>361.33</v>
       </c>
       <c r="E92" t="n">
-        <v>1250</v>
+        <v>957</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>46061</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>004</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2467,54 +2467,54 @@
         <v>213</v>
       </c>
       <c r="D93" t="n">
-        <v>361.33</v>
+        <v>426.67</v>
       </c>
       <c r="E93" t="n">
-        <v>957</v>
+        <v>531</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>157</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C94" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D94" t="n">
-        <v>426.67</v>
+        <v>139.45</v>
       </c>
       <c r="E94" t="n">
-        <v>531</v>
+        <v>426</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>46065</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>245</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C95" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D95" t="n">
-        <v>139.45</v>
+        <v>163.33</v>
       </c>
       <c r="E95" t="n">
-        <v>426</v>
+        <v>498</v>
       </c>
       <c r="F95" s="1" t="n">
         <v>46067</v>
@@ -2523,86 +2523,86 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C96" t="n">
         <v>206</v>
       </c>
       <c r="D96" t="n">
-        <v>163.33</v>
+        <v>190</v>
       </c>
       <c r="E96" t="n">
-        <v>498</v>
+        <v>700</v>
       </c>
       <c r="F96" s="1" t="n">
-        <v>46067</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>166</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C97" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D97" t="n">
-        <v>190</v>
+        <v>154.83</v>
       </c>
       <c r="E97" t="n">
-        <v>700</v>
+        <v>256</v>
       </c>
       <c r="F97" s="1" t="n">
-        <v>46068</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>579</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C98" t="n">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D98" t="n">
-        <v>154.83</v>
+        <v>223</v>
       </c>
       <c r="E98" t="n">
-        <v>256</v>
+        <v>455</v>
       </c>
       <c r="F98" s="1" t="n">
-        <v>46071</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>488</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>8</v>
       </c>
       <c r="C99" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D99" t="n">
-        <v>223</v>
+        <v>222.43</v>
       </c>
       <c r="E99" t="n">
-        <v>455</v>
+        <v>560</v>
       </c>
       <c r="F99" s="1" t="n">
         <v>46077</v>
@@ -2611,42 +2611,42 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>8</v>
       </c>
       <c r="C100" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D100" t="n">
-        <v>222.43</v>
+        <v>206.71</v>
       </c>
       <c r="E100" t="n">
-        <v>560</v>
+        <v>692</v>
       </c>
       <c r="F100" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>479</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C101" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D101" t="n">
-        <v>206.71</v>
+        <v>261.8</v>
       </c>
       <c r="E101" t="n">
-        <v>692</v>
+        <v>623</v>
       </c>
       <c r="F101" s="1" t="n">
         <v>46078</v>
@@ -2655,42 +2655,42 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C102" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D102" t="n">
-        <v>261.8</v>
+        <v>159.88</v>
       </c>
       <c r="E102" t="n">
-        <v>623</v>
+        <v>360</v>
       </c>
       <c r="F102" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C103" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D103" t="n">
-        <v>159.88</v>
+        <v>138.3</v>
       </c>
       <c r="E103" t="n">
-        <v>360</v>
+        <v>445</v>
       </c>
       <c r="F103" s="1" t="n">
         <v>46079</v>
@@ -2699,130 +2699,130 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C104" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D104" t="n">
-        <v>138.3</v>
+        <v>110.92</v>
       </c>
       <c r="E104" t="n">
-        <v>445</v>
+        <v>362</v>
       </c>
       <c r="F104" s="1" t="n">
-        <v>46079</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>458</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C105" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D105" t="n">
-        <v>110.92</v>
+        <v>156.4</v>
       </c>
       <c r="E105" t="n">
-        <v>362</v>
+        <v>436</v>
       </c>
       <c r="F105" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C106" t="n">
         <v>171</v>
       </c>
       <c r="D106" t="n">
-        <v>156.4</v>
+        <v>186.12</v>
       </c>
       <c r="E106" t="n">
-        <v>436</v>
+        <v>533</v>
       </c>
       <c r="F106" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>268</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C107" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D107" t="n">
-        <v>186.12</v>
+        <v>235.5</v>
       </c>
       <c r="E107" t="n">
-        <v>533</v>
+        <v>676</v>
       </c>
       <c r="F107" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C108" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D108" t="n">
-        <v>235.5</v>
+        <v>168</v>
       </c>
       <c r="E108" t="n">
-        <v>676</v>
+        <v>394</v>
       </c>
       <c r="F108" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>023</t>
+          <t>167</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C109" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D109" t="n">
-        <v>168</v>
+        <v>119.55</v>
       </c>
       <c r="E109" t="n">
-        <v>394</v>
+        <v>271</v>
       </c>
       <c r="F109" s="1" t="n">
         <v>46090</v>
@@ -2831,108 +2831,108 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C110" t="n">
         <v>160</v>
       </c>
       <c r="D110" t="n">
-        <v>119.55</v>
+        <v>226.71</v>
       </c>
       <c r="E110" t="n">
-        <v>271</v>
+        <v>729</v>
       </c>
       <c r="F110" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>099</t>
+          <t>388</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C111" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D111" t="n">
-        <v>226.71</v>
+        <v>358.5</v>
       </c>
       <c r="E111" t="n">
-        <v>729</v>
+        <v>1126</v>
       </c>
       <c r="F111" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>257</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C112" t="n">
         <v>157</v>
       </c>
       <c r="D112" t="n">
-        <v>358.5</v>
+        <v>131.75</v>
       </c>
       <c r="E112" t="n">
-        <v>1126</v>
+        <v>388</v>
       </c>
       <c r="F112" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>234</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C113" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D113" t="n">
-        <v>131.75</v>
+        <v>107.29</v>
       </c>
       <c r="E113" t="n">
-        <v>388</v>
+        <v>245</v>
       </c>
       <c r="F113" s="1" t="n">
-        <v>46093</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>247</t>
         </is>
       </c>
       <c r="B114" t="n">
         <v>15</v>
       </c>
       <c r="C114" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D114" t="n">
-        <v>107.29</v>
+        <v>107.93</v>
       </c>
       <c r="E114" t="n">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="F114" s="1" t="n">
         <v>46095</v>
@@ -2941,86 +2941,86 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>012</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C115" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D115" t="n">
-        <v>107.93</v>
+        <v>162.88</v>
       </c>
       <c r="E115" t="n">
-        <v>210</v>
+        <v>544</v>
       </c>
       <c r="F115" s="1" t="n">
-        <v>46095</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>668</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C116" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D116" t="n">
-        <v>162.88</v>
+        <v>96</v>
       </c>
       <c r="E116" t="n">
-        <v>544</v>
+        <v>115</v>
       </c>
       <c r="F116" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>688</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C117" t="n">
         <v>141</v>
       </c>
       <c r="D117" t="n">
-        <v>96</v>
+        <v>236.83</v>
       </c>
       <c r="E117" t="n">
-        <v>115</v>
+        <v>461</v>
       </c>
       <c r="F117" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>337</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C118" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D118" t="n">
-        <v>236.83</v>
+        <v>326.75</v>
       </c>
       <c r="E118" t="n">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F118" s="1" t="n">
         <v>46101</v>
@@ -3029,86 +3029,86 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C119" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D119" t="n">
-        <v>326.75</v>
+        <v>204.71</v>
       </c>
       <c r="E119" t="n">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="F119" s="1" t="n">
-        <v>46101</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>059</t>
+          <t>678</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C120" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D120" t="n">
-        <v>204.71</v>
+        <v>121.25</v>
       </c>
       <c r="E120" t="n">
-        <v>492</v>
+        <v>321</v>
       </c>
       <c r="F120" s="1" t="n">
-        <v>46102</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>038</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C121" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D121" t="n">
-        <v>121.25</v>
+        <v>130.73</v>
       </c>
       <c r="E121" t="n">
-        <v>321</v>
+        <v>467</v>
       </c>
       <c r="F121" s="1" t="n">
-        <v>46103</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>038</t>
+          <t>589</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C122" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D122" t="n">
-        <v>130.73</v>
+        <v>243.83</v>
       </c>
       <c r="E122" t="n">
-        <v>467</v>
+        <v>546</v>
       </c>
       <c r="F122" s="1" t="n">
         <v>46104</v>
@@ -3117,64 +3117,64 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>228</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C123" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D123" t="n">
-        <v>243.83</v>
+        <v>277</v>
       </c>
       <c r="E123" t="n">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="F123" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C124" t="n">
         <v>131</v>
       </c>
       <c r="D124" t="n">
-        <v>277</v>
+        <v>225.83</v>
       </c>
       <c r="E124" t="n">
-        <v>536</v>
+        <v>474</v>
       </c>
       <c r="F124" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>006</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C125" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D125" t="n">
-        <v>225.83</v>
+        <v>489.67</v>
       </c>
       <c r="E125" t="n">
-        <v>474</v>
+        <v>714</v>
       </c>
       <c r="F125" s="1" t="n">
         <v>46106</v>
@@ -3183,86 +3183,86 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C126" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D126" t="n">
-        <v>489.67</v>
+        <v>131.09</v>
       </c>
       <c r="E126" t="n">
-        <v>714</v>
+        <v>257</v>
       </c>
       <c r="F126" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>089</t>
+          <t>259</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C127" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D127" t="n">
-        <v>131.09</v>
+        <v>160</v>
       </c>
       <c r="E127" t="n">
-        <v>257</v>
+        <v>502</v>
       </c>
       <c r="F127" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C128" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D128" t="n">
-        <v>160</v>
+        <v>280.8</v>
       </c>
       <c r="E128" t="n">
-        <v>502</v>
+        <v>448</v>
       </c>
       <c r="F128" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C129" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D129" t="n">
-        <v>280.8</v>
+        <v>1368</v>
       </c>
       <c r="E129" t="n">
-        <v>448</v>
+        <v>1368</v>
       </c>
       <c r="F129" s="1" t="n">
         <v>46110</v>
@@ -3271,51 +3271,51 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>457</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C130" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D130" t="n">
-        <v>1368</v>
+        <v>110.09</v>
       </c>
       <c r="E130" t="n">
-        <v>1368</v>
+        <v>266</v>
       </c>
       <c r="F130" s="1" t="n">
-        <v>46110</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>034</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C131" t="n">
         <v>115</v>
       </c>
       <c r="D131" t="n">
-        <v>110.09</v>
+        <v>352</v>
       </c>
       <c r="E131" t="n">
-        <v>266</v>
+        <v>704</v>
       </c>
       <c r="F131" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>034</t>
+          <t>277</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3325,32 +3325,32 @@
         <v>113</v>
       </c>
       <c r="D132" t="n">
-        <v>352</v>
+        <v>405.75</v>
       </c>
       <c r="E132" t="n">
-        <v>704</v>
+        <v>986</v>
       </c>
       <c r="F132" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>255</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C133" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D133" t="n">
-        <v>405.75</v>
+        <v>442.33</v>
       </c>
       <c r="E133" t="n">
-        <v>986</v>
+        <v>776</v>
       </c>
       <c r="F133" s="1" t="n">
         <v>46115</v>
@@ -3359,108 +3359,108 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>036</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C134" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D134" t="n">
-        <v>442.33</v>
+        <v>100.4</v>
       </c>
       <c r="E134" t="n">
-        <v>776</v>
+        <v>309</v>
       </c>
       <c r="F134" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>036</t>
+          <t>016</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C135" t="n">
         <v>107</v>
       </c>
       <c r="D135" t="n">
-        <v>100.4</v>
+        <v>237.67</v>
       </c>
       <c r="E135" t="n">
-        <v>309</v>
+        <v>549</v>
       </c>
       <c r="F135" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C136" t="n">
         <v>105</v>
       </c>
       <c r="D136" t="n">
-        <v>237.67</v>
+        <v>131.45</v>
       </c>
       <c r="E136" t="n">
-        <v>549</v>
+        <v>317</v>
       </c>
       <c r="F136" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>056</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C137" t="n">
         <v>103</v>
       </c>
       <c r="D137" t="n">
-        <v>131.45</v>
+        <v>124.77</v>
       </c>
       <c r="E137" t="n">
-        <v>317</v>
+        <v>363</v>
       </c>
       <c r="F137" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>024</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C138" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D138" t="n">
-        <v>124.77</v>
+        <v>385.33</v>
       </c>
       <c r="E138" t="n">
-        <v>363</v>
+        <v>1014</v>
       </c>
       <c r="F138" s="1" t="n">
         <v>46120</v>
@@ -3469,86 +3469,86 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>235</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C139" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D139" t="n">
-        <v>385.33</v>
+        <v>102.7</v>
       </c>
       <c r="E139" t="n">
-        <v>1014</v>
+        <v>185</v>
       </c>
       <c r="F139" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>469</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C140" t="n">
         <v>99</v>
       </c>
       <c r="D140" t="n">
-        <v>102.7</v>
+        <v>105</v>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>311</v>
       </c>
       <c r="F140" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C141" t="n">
         <v>97</v>
       </c>
       <c r="D141" t="n">
-        <v>105</v>
+        <v>350</v>
       </c>
       <c r="E141" t="n">
-        <v>311</v>
+        <v>593</v>
       </c>
       <c r="F141" s="1" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>889</t>
         </is>
       </c>
       <c r="B142" t="n">
         <v>4</v>
       </c>
       <c r="C142" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D142" t="n">
-        <v>350</v>
+        <v>527.67</v>
       </c>
       <c r="E142" t="n">
-        <v>593</v>
+        <v>1098</v>
       </c>
       <c r="F142" s="1" t="n">
         <v>46123</v>
@@ -3557,42 +3557,42 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>368</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C143" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D143" t="n">
-        <v>527.67</v>
+        <v>179.44</v>
       </c>
       <c r="E143" t="n">
-        <v>1098</v>
+        <v>682</v>
       </c>
       <c r="F143" s="1" t="n">
-        <v>46123</v>
+        <v>46124</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>278</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C144" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D144" t="n">
-        <v>179.44</v>
+        <v>204.5</v>
       </c>
       <c r="E144" t="n">
-        <v>682</v>
+        <v>570</v>
       </c>
       <c r="F144" s="1" t="n">
         <v>46124</v>
@@ -3601,117 +3601,117 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C145" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D145" t="n">
-        <v>204.5</v>
+        <v>134.75</v>
       </c>
       <c r="E145" t="n">
-        <v>570</v>
+        <v>684</v>
       </c>
       <c r="F145" s="1" t="n">
-        <v>46124</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>049</t>
+          <t>289</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C146" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D146" t="n">
-        <v>123.62</v>
+        <v>180.44</v>
       </c>
       <c r="E146" t="n">
-        <v>238</v>
+        <v>632</v>
       </c>
       <c r="F146" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>057</t>
+          <t>258</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C147" t="n">
         <v>89</v>
       </c>
       <c r="D147" t="n">
-        <v>134.75</v>
+        <v>160.2</v>
       </c>
       <c r="E147" t="n">
-        <v>684</v>
+        <v>348</v>
       </c>
       <c r="F147" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C148" t="n">
         <v>88</v>
       </c>
       <c r="D148" t="n">
-        <v>180.44</v>
+        <v>236.29</v>
       </c>
       <c r="E148" t="n">
-        <v>632</v>
+        <v>568</v>
       </c>
       <c r="F148" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C149" t="n">
         <v>87</v>
       </c>
       <c r="D149" t="n">
-        <v>160.2</v>
+        <v>322.2</v>
       </c>
       <c r="E149" t="n">
-        <v>348</v>
+        <v>773</v>
       </c>
       <c r="F149" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3721,327 +3721,327 @@
         <v>86</v>
       </c>
       <c r="D150" t="n">
-        <v>236.29</v>
+        <v>212</v>
       </c>
       <c r="E150" t="n">
-        <v>568</v>
+        <v>526</v>
       </c>
       <c r="F150" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>079</t>
+          <t>269</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C151" t="n">
         <v>85</v>
       </c>
       <c r="D151" t="n">
-        <v>322.2</v>
+        <v>128.67</v>
       </c>
       <c r="E151" t="n">
-        <v>773</v>
+        <v>296</v>
       </c>
       <c r="F151" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>246</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C152" t="n">
         <v>84</v>
       </c>
       <c r="D152" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E152" t="n">
-        <v>526</v>
+        <v>717</v>
       </c>
       <c r="F152" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>022</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C153" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D153" t="n">
-        <v>128.67</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="F153" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>058</t>
         </is>
       </c>
       <c r="B154" t="n">
         <v>9</v>
       </c>
       <c r="C154" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D154" t="n">
-        <v>208</v>
+        <v>187.38</v>
       </c>
       <c r="E154" t="n">
-        <v>717</v>
+        <v>511</v>
       </c>
       <c r="F154" s="1" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>022</t>
+          <t>378</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C155" t="n">
         <v>80</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>255.6</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>742</v>
       </c>
       <c r="F155" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>058</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C156" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D156" t="n">
-        <v>187.38</v>
+        <v>164.43</v>
       </c>
       <c r="E156" t="n">
-        <v>511</v>
+        <v>470</v>
       </c>
       <c r="F156" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>238</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C157" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D157" t="n">
-        <v>255.6</v>
+        <v>111.46</v>
       </c>
       <c r="E157" t="n">
-        <v>742</v>
+        <v>520</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>46131</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>568</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C158" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D158" t="n">
-        <v>164.43</v>
+        <v>103.75</v>
       </c>
       <c r="E158" t="n">
-        <v>470</v>
+        <v>275</v>
       </c>
       <c r="F158" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>569</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C159" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D159" t="n">
-        <v>111.46</v>
+        <v>173.22</v>
       </c>
       <c r="E159" t="n">
-        <v>520</v>
+        <v>582</v>
       </c>
       <c r="F159" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C160" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D160" t="n">
-        <v>103.75</v>
+        <v>233.29</v>
       </c>
       <c r="E160" t="n">
-        <v>275</v>
+        <v>741</v>
       </c>
       <c r="F160" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>349</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C161" t="n">
         <v>71</v>
       </c>
       <c r="D161" t="n">
-        <v>173.22</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="E161" t="n">
-        <v>582</v>
+        <v>303</v>
       </c>
       <c r="F161" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>226</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C162" t="n">
         <v>70</v>
       </c>
       <c r="D162" t="n">
-        <v>233.29</v>
+        <v>232.6</v>
       </c>
       <c r="E162" t="n">
-        <v>741</v>
+        <v>514</v>
       </c>
       <c r="F162" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C163" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D163" t="n">
-        <v>93.23999999999999</v>
+        <v>131.82</v>
       </c>
       <c r="E163" t="n">
-        <v>303</v>
+        <v>396</v>
       </c>
       <c r="F163" s="1" t="n">
-        <v>46136</v>
+        <v>46138</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C164" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D164" t="n">
-        <v>232.6</v>
+        <v>209.25</v>
       </c>
       <c r="E164" t="n">
-        <v>514</v>
+        <v>742</v>
       </c>
       <c r="F164" s="1" t="n">
-        <v>46136</v>
+        <v>46138</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>357</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -4051,723 +4051,723 @@
         <v>65</v>
       </c>
       <c r="D165" t="n">
-        <v>131.82</v>
+        <v>140.64</v>
       </c>
       <c r="E165" t="n">
-        <v>396</v>
+        <v>240</v>
       </c>
       <c r="F165" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C166" t="n">
         <v>64</v>
       </c>
       <c r="D166" t="n">
-        <v>209.25</v>
+        <v>201</v>
       </c>
       <c r="E166" t="n">
-        <v>742</v>
+        <v>772</v>
       </c>
       <c r="F166" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C167" t="n">
         <v>63</v>
       </c>
       <c r="D167" t="n">
-        <v>140.64</v>
+        <v>147.5</v>
       </c>
       <c r="E167" t="n">
-        <v>240</v>
+        <v>399</v>
       </c>
       <c r="F167" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C168" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D168" t="n">
-        <v>201</v>
+        <v>334.6</v>
       </c>
       <c r="E168" t="n">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="F168" s="1" t="n">
-        <v>46139</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C169" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D169" t="n">
-        <v>147.5</v>
+        <v>206.6</v>
       </c>
       <c r="E169" t="n">
-        <v>399</v>
+        <v>464</v>
       </c>
       <c r="F169" s="1" t="n">
-        <v>46140</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>237</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C170" t="n">
         <v>56</v>
       </c>
       <c r="D170" t="n">
-        <v>334.6</v>
+        <v>121.64</v>
       </c>
       <c r="E170" t="n">
-        <v>784</v>
+        <v>214</v>
       </c>
       <c r="F170" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>345</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C171" t="n">
         <v>55</v>
       </c>
       <c r="D171" t="n">
-        <v>206.6</v>
+        <v>115.25</v>
       </c>
       <c r="E171" t="n">
-        <v>464</v>
+        <v>365</v>
       </c>
       <c r="F171" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C172" t="n">
         <v>54</v>
       </c>
       <c r="D172" t="n">
-        <v>121.64</v>
+        <v>234.71</v>
       </c>
       <c r="E172" t="n">
-        <v>214</v>
+        <v>547</v>
       </c>
       <c r="F172" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C173" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D173" t="n">
-        <v>115.25</v>
+        <v>261.5</v>
       </c>
       <c r="E173" t="n">
-        <v>365</v>
+        <v>441</v>
       </c>
       <c r="F173" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>267</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C174" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D174" t="n">
-        <v>234.71</v>
+        <v>286.8</v>
       </c>
       <c r="E174" t="n">
-        <v>547</v>
+        <v>804</v>
       </c>
       <c r="F174" s="1" t="n">
-        <v>46144</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>045</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C175" t="n">
         <v>50</v>
       </c>
       <c r="D175" t="n">
-        <v>261.5</v>
+        <v>174.44</v>
       </c>
       <c r="E175" t="n">
-        <v>441</v>
+        <v>550</v>
       </c>
       <c r="F175" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C176" t="n">
         <v>49</v>
       </c>
       <c r="D176" t="n">
-        <v>286.8</v>
+        <v>115.64</v>
       </c>
       <c r="E176" t="n">
-        <v>804</v>
+        <v>303</v>
       </c>
       <c r="F176" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C177" t="n">
         <v>48</v>
       </c>
       <c r="D177" t="n">
-        <v>174.44</v>
+        <v>112.85</v>
       </c>
       <c r="E177" t="n">
-        <v>550</v>
+        <v>451</v>
       </c>
       <c r="F177" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>067</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C178" t="n">
         <v>47</v>
       </c>
       <c r="D178" t="n">
-        <v>115.64</v>
+        <v>131.08</v>
       </c>
       <c r="E178" t="n">
-        <v>303</v>
+        <v>541</v>
       </c>
       <c r="F178" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C179" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D179" t="n">
-        <v>112.85</v>
+        <v>113.87</v>
       </c>
       <c r="E179" t="n">
-        <v>451</v>
+        <v>307</v>
       </c>
       <c r="F179" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C180" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D180" t="n">
-        <v>131.08</v>
+        <v>107.5</v>
       </c>
       <c r="E180" t="n">
-        <v>541</v>
+        <v>427</v>
       </c>
       <c r="F180" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>288</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C181" t="n">
         <v>43</v>
       </c>
       <c r="D181" t="n">
-        <v>113.87</v>
+        <v>276.33</v>
       </c>
       <c r="E181" t="n">
-        <v>307</v>
+        <v>779</v>
       </c>
       <c r="F181" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C182" t="n">
         <v>42</v>
       </c>
       <c r="D182" t="n">
-        <v>107.5</v>
+        <v>120.36</v>
       </c>
       <c r="E182" t="n">
-        <v>427</v>
+        <v>359</v>
       </c>
       <c r="F182" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>145</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C183" t="n">
         <v>41</v>
       </c>
       <c r="D183" t="n">
-        <v>276.33</v>
+        <v>191.29</v>
       </c>
       <c r="E183" t="n">
-        <v>779</v>
+        <v>336</v>
       </c>
       <c r="F183" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C184" t="n">
         <v>40</v>
       </c>
       <c r="D184" t="n">
-        <v>120.36</v>
+        <v>106.43</v>
       </c>
       <c r="E184" t="n">
-        <v>359</v>
+        <v>190</v>
       </c>
       <c r="F184" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>239</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D185" t="n">
-        <v>191.29</v>
+        <v>99.8</v>
       </c>
       <c r="E185" t="n">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="F185" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>249</t>
         </is>
       </c>
       <c r="B186" t="n">
         <v>8</v>
       </c>
       <c r="C186" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D186" t="n">
-        <v>106.43</v>
+        <v>195.29</v>
       </c>
       <c r="E186" t="n">
-        <v>190</v>
+        <v>779</v>
       </c>
       <c r="F186" s="1" t="n">
-        <v>46151</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>577</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C187" t="n">
         <v>36</v>
       </c>
       <c r="D187" t="n">
-        <v>99.8</v>
+        <v>233</v>
       </c>
       <c r="E187" t="n">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="F187" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C188" t="n">
         <v>35</v>
       </c>
       <c r="D188" t="n">
-        <v>195.29</v>
+        <v>214.62</v>
       </c>
       <c r="E188" t="n">
-        <v>779</v>
+        <v>365</v>
       </c>
       <c r="F188" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>466</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C189" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D189" t="n">
-        <v>233</v>
+        <v>182.88</v>
       </c>
       <c r="E189" t="n">
-        <v>281</v>
+        <v>326</v>
       </c>
       <c r="F189" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C190" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D190" t="n">
-        <v>214.62</v>
+        <v>127</v>
       </c>
       <c r="E190" t="n">
-        <v>365</v>
+        <v>455</v>
       </c>
       <c r="F190" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>467</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C191" t="n">
         <v>31</v>
       </c>
       <c r="D191" t="n">
-        <v>182.88</v>
+        <v>147.3</v>
       </c>
       <c r="E191" t="n">
-        <v>326</v>
+        <v>506</v>
       </c>
       <c r="F191" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>078</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C192" t="n">
         <v>30</v>
       </c>
       <c r="D192" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E192" t="n">
-        <v>455</v>
+        <v>420</v>
       </c>
       <c r="F192" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>358</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C193" t="n">
         <v>29</v>
       </c>
       <c r="D193" t="n">
-        <v>147.3</v>
+        <v>360</v>
       </c>
       <c r="E193" t="n">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="F193" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>078</t>
+          <t>369</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C194" t="n">
         <v>28</v>
       </c>
       <c r="D194" t="n">
-        <v>119</v>
+        <v>133.5</v>
       </c>
       <c r="E194" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F194" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>468</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C195" t="n">
         <v>27</v>
       </c>
       <c r="D195" t="n">
-        <v>360</v>
+        <v>112.8</v>
       </c>
       <c r="E195" t="n">
-        <v>483</v>
+        <v>331</v>
       </c>
       <c r="F195" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C196" t="n">
         <v>26</v>
       </c>
       <c r="D196" t="n">
-        <v>133.5</v>
+        <v>182.12</v>
       </c>
       <c r="E196" t="n">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="F196" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>366</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C197" t="n">
         <v>25</v>
       </c>
       <c r="D197" t="n">
-        <v>112.8</v>
+        <v>248</v>
       </c>
       <c r="E197" t="n">
-        <v>331</v>
+        <v>658</v>
       </c>
       <c r="F197" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4777,519 +4777,519 @@
         <v>24</v>
       </c>
       <c r="D198" t="n">
-        <v>182.12</v>
+        <v>199.12</v>
       </c>
       <c r="E198" t="n">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F198" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C199" t="n">
         <v>23</v>
       </c>
       <c r="D199" t="n">
-        <v>248</v>
+        <v>452</v>
       </c>
       <c r="E199" t="n">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="F199" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>389</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C200" t="n">
         <v>22</v>
       </c>
       <c r="D200" t="n">
-        <v>199.12</v>
+        <v>134.5</v>
       </c>
       <c r="E200" t="n">
-        <v>441</v>
+        <v>490</v>
       </c>
       <c r="F200" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>026</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C201" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D201" t="n">
-        <v>452</v>
+        <v>135</v>
       </c>
       <c r="E201" t="n">
-        <v>661</v>
+        <v>403</v>
       </c>
       <c r="F201" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C202" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D202" t="n">
-        <v>134.5</v>
+        <v>245</v>
       </c>
       <c r="E202" t="n">
-        <v>490</v>
+        <v>518</v>
       </c>
       <c r="F202" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>026</t>
+          <t>588</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C203" t="n">
         <v>18</v>
       </c>
       <c r="D203" t="n">
-        <v>135</v>
+        <v>355.67</v>
       </c>
       <c r="E203" t="n">
-        <v>403</v>
+        <v>620</v>
       </c>
       <c r="F203" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>799</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C204" t="n">
         <v>17</v>
       </c>
       <c r="D204" t="n">
-        <v>245</v>
+        <v>146.1</v>
       </c>
       <c r="E204" t="n">
-        <v>518</v>
+        <v>372</v>
       </c>
       <c r="F204" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C205" t="n">
         <v>16</v>
       </c>
       <c r="D205" t="n">
-        <v>355.67</v>
+        <v>228.83</v>
       </c>
       <c r="E205" t="n">
-        <v>620</v>
+        <v>499</v>
       </c>
       <c r="F205" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C206" t="n">
         <v>15</v>
       </c>
       <c r="D206" t="n">
-        <v>146.1</v>
+        <v>169.33</v>
       </c>
       <c r="E206" t="n">
-        <v>372</v>
+        <v>300</v>
       </c>
       <c r="F206" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>669</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C207" t="n">
         <v>14</v>
       </c>
       <c r="D207" t="n">
-        <v>228.83</v>
+        <v>313.8</v>
       </c>
       <c r="E207" t="n">
-        <v>499</v>
+        <v>608</v>
       </c>
       <c r="F207" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C208" t="n">
         <v>13</v>
       </c>
       <c r="D208" t="n">
-        <v>169.33</v>
+        <v>172</v>
       </c>
       <c r="E208" t="n">
-        <v>300</v>
+        <v>349</v>
       </c>
       <c r="F208" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C209" t="n">
         <v>12</v>
       </c>
       <c r="D209" t="n">
-        <v>313.8</v>
+        <v>109.93</v>
       </c>
       <c r="E209" t="n">
-        <v>608</v>
+        <v>724</v>
       </c>
       <c r="F209" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C210" t="n">
         <v>11</v>
       </c>
       <c r="D210" t="n">
-        <v>172</v>
+        <v>429</v>
       </c>
       <c r="E210" t="n">
-        <v>349</v>
+        <v>742</v>
       </c>
       <c r="F210" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>148</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C211" t="n">
         <v>10</v>
       </c>
       <c r="D211" t="n">
-        <v>109.93</v>
+        <v>88.42</v>
       </c>
       <c r="E211" t="n">
-        <v>724</v>
+        <v>311</v>
       </c>
       <c r="F211" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>068</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C212" t="n">
         <v>9</v>
       </c>
       <c r="D212" t="n">
-        <v>429</v>
+        <v>236.67</v>
       </c>
       <c r="E212" t="n">
-        <v>742</v>
+        <v>652</v>
       </c>
       <c r="F212" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>679</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C213" t="n">
         <v>8</v>
       </c>
       <c r="D213" t="n">
-        <v>88.42</v>
+        <v>233.43</v>
       </c>
       <c r="E213" t="n">
-        <v>311</v>
+        <v>593</v>
       </c>
       <c r="F213" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>046</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C214" t="n">
         <v>7</v>
       </c>
       <c r="D214" t="n">
-        <v>236.67</v>
+        <v>113.93</v>
       </c>
       <c r="E214" t="n">
-        <v>652</v>
+        <v>306</v>
       </c>
       <c r="F214" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C215" t="n">
         <v>6</v>
       </c>
       <c r="D215" t="n">
-        <v>233.43</v>
+        <v>126.77</v>
       </c>
       <c r="E215" t="n">
-        <v>593</v>
+        <v>336</v>
       </c>
       <c r="F215" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>046</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C216" t="n">
         <v>5</v>
       </c>
       <c r="D216" t="n">
-        <v>113.93</v>
+        <v>208.88</v>
       </c>
       <c r="E216" t="n">
-        <v>306</v>
+        <v>408</v>
       </c>
       <c r="F216" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>037</t>
+          <t>558</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C217" t="n">
         <v>4</v>
       </c>
       <c r="D217" t="n">
-        <v>126.77</v>
+        <v>430.67</v>
       </c>
       <c r="E217" t="n">
-        <v>336</v>
+        <v>570</v>
       </c>
       <c r="F217" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C218" t="n">
         <v>3</v>
       </c>
       <c r="D218" t="n">
-        <v>208.88</v>
+        <v>154.18</v>
       </c>
       <c r="E218" t="n">
-        <v>408</v>
+        <v>538</v>
       </c>
       <c r="F218" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C219" t="n">
         <v>2</v>
       </c>
       <c r="D219" t="n">
-        <v>430.67</v>
+        <v>155.91</v>
       </c>
       <c r="E219" t="n">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="F219" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>154.18</v>
+        <v>121.36</v>
       </c>
       <c r="E220" t="n">
-        <v>538</v>
+        <v>238</v>
       </c>
       <c r="F220" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>155.91</v>
+        <v>243.14</v>
       </c>
       <c r="E221" t="n">
-        <v>551</v>
+        <v>687</v>
       </c>
       <c r="F221" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
     </row>
   </sheetData>
